--- a/output/roomself_excel/7727.xlsx
+++ b/output/roomself_excel/7727.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>117949</v>
+        <v>329123</v>
       </c>
       <c r="D2" t="n">
-        <v>3080</v>
+        <v>5656</v>
       </c>
       <c r="E2" t="n">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="F2" t="n">
-        <v>228</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>261580</v>
+        <v>918742</v>
       </c>
       <c r="D3" t="n">
-        <v>4124</v>
+        <v>10028</v>
       </c>
       <c r="E3" t="n">
-        <v>623</v>
+        <v>1386</v>
       </c>
       <c r="F3" t="n">
-        <v>495</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>918742</v>
+        <v>261580</v>
       </c>
       <c r="D4" t="n">
-        <v>10028</v>
+        <v>4124</v>
       </c>
       <c r="E4" t="n">
-        <v>1386</v>
+        <v>623</v>
       </c>
       <c r="F4" t="n">
-        <v>272</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>978696</v>
+        <v>336400</v>
       </c>
       <c r="D5" t="n">
-        <v>7936</v>
+        <v>4640</v>
       </c>
       <c r="E5" t="n">
-        <v>1432</v>
+        <v>624</v>
       </c>
       <c r="F5" t="n">
-        <v>975</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>228684</v>
+        <v>70736</v>
       </c>
       <c r="D6" t="n">
-        <v>5300</v>
+        <v>2316</v>
       </c>
       <c r="E6" t="n">
-        <v>1165</v>
+        <v>334</v>
       </c>
       <c r="F6" t="n">
-        <v>249</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>355968</v>
+        <v>117949</v>
       </c>
       <c r="D7" t="n">
-        <v>4776</v>
+        <v>3080</v>
       </c>
       <c r="E7" t="n">
-        <v>878</v>
+        <v>595</v>
       </c>
       <c r="F7" t="n">
-        <v>576</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>303774</v>
+        <v>121042</v>
       </c>
       <c r="D8" t="n">
-        <v>7516</v>
+        <v>5899</v>
       </c>
       <c r="E8" t="n">
-        <v>1143</v>
+        <v>216</v>
       </c>
       <c r="F8" t="n">
-        <v>473</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>737100</v>
+        <v>1345</v>
       </c>
       <c r="D9" t="n">
-        <v>7012</v>
+        <v>581</v>
       </c>
       <c r="E9" t="n">
-        <v>1143</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>345644</v>
+        <v>978696</v>
       </c>
       <c r="D10" t="n">
-        <v>4704</v>
+        <v>7936</v>
       </c>
       <c r="E10" t="n">
-        <v>598</v>
+        <v>1138</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>975</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>137016</v>
+        <v>228684</v>
       </c>
       <c r="D11" t="n">
-        <v>3132</v>
+        <v>5300</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1165</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>143013</v>
+        <v>355968</v>
       </c>
       <c r="D12" t="n">
-        <v>3304</v>
+        <v>4776</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>748</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>336400</v>
+        <v>303774</v>
       </c>
       <c r="D13" t="n">
-        <v>4640</v>
+        <v>7516</v>
       </c>
       <c r="E13" t="n">
-        <v>914</v>
+        <v>1143</v>
       </c>
       <c r="F13" t="n">
-        <v>440</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37389</v>
+        <v>737100</v>
       </c>
       <c r="D14" t="n">
-        <v>1720</v>
+        <v>7012</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1143</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>121042</v>
+        <v>345644</v>
       </c>
       <c r="D15" t="n">
-        <v>5899</v>
+        <v>4704</v>
       </c>
       <c r="E15" t="n">
-        <v>335</v>
+        <v>598</v>
       </c>
       <c r="F15" t="n">
-        <v>265</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>108329</v>
+        <v>137016</v>
       </c>
       <c r="D16" t="n">
-        <v>3964</v>
+        <v>3132</v>
       </c>
       <c r="E16" t="n">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>329123</v>
+        <v>143013</v>
       </c>
       <c r="D17" t="n">
-        <v>5656</v>
+        <v>3304</v>
       </c>
       <c r="E17" t="n">
-        <v>582</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>64272</v>
+        <v>37389</v>
       </c>
       <c r="D18" t="n">
-        <v>2068</v>
+        <v>1720</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>418030</v>
+        <v>108329</v>
       </c>
       <c r="D19" t="n">
-        <v>10240</v>
+        <v>3964</v>
       </c>
       <c r="E19" t="n">
-        <v>748</v>
+        <v>383</v>
       </c>
       <c r="F19" t="n">
-        <v>334</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20">
@@ -862,14 +862,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1345</v>
+        <v>64272</v>
       </c>
       <c r="D20" t="n">
-        <v>581</v>
+        <v>2068</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23465</v>
+        <v>418030</v>
       </c>
       <c r="D21" t="n">
-        <v>1368</v>
+        <v>10240</v>
       </c>
       <c r="E21" t="n">
-        <v>95</v>
+        <v>554</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>165499</v>
+        <v>23465</v>
       </c>
       <c r="D22" t="n">
-        <v>5028</v>
+        <v>1368</v>
       </c>
       <c r="E22" t="n">
-        <v>1139</v>
+        <v>95</v>
       </c>
       <c r="F22" t="n">
-        <v>207</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13110</v>
+        <v>165499</v>
       </c>
       <c r="D23" t="n">
-        <v>932</v>
+        <v>5028</v>
       </c>
       <c r="E23" t="n">
-        <v>208</v>
+        <v>1139</v>
       </c>
       <c r="F23" t="n">
-        <v>95</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>39812</v>
+        <v>13110</v>
       </c>
       <c r="D24" t="n">
-        <v>1636</v>
+        <v>932</v>
       </c>
       <c r="E24" t="n">
-        <v>335</v>
+        <v>208</v>
       </c>
       <c r="F24" t="n">
-        <v>160</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>51225</v>
+        <v>39812</v>
       </c>
       <c r="D25" t="n">
-        <v>1820</v>
+        <v>1636</v>
       </c>
       <c r="E25" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F25" t="n">
-        <v>249</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26">
@@ -994,20 +994,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>70736</v>
+        <v>51225</v>
       </c>
       <c r="D26" t="n">
-        <v>2316</v>
+        <v>1820</v>
       </c>
       <c r="E26" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F26" t="n">
-        <v>289</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27">

--- a/output/roomself_excel/7727.xlsx
+++ b/output/roomself_excel/7727.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,23 @@
       <c r="D2" t="n">
         <v>5656</v>
       </c>
-      <c r="E2" t="n">
-        <v>582</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>335</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="G2" t="n">
+        <v>44</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +543,23 @@
       <c r="D3" t="n">
         <v>10028</v>
       </c>
-      <c r="E3" t="n">
-        <v>1386</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
-      </c>
+        <v>791</v>
+      </c>
+      <c r="G3" t="n">
+        <v>44</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +576,31 @@
       <c r="D4" t="n">
         <v>4124</v>
       </c>
-      <c r="E4" t="n">
-        <v>623</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>495</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="G4" t="n">
+        <v>44</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>451</v>
+      </c>
+      <c r="J4" t="n">
+        <v>43</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +617,31 @@
       <c r="D5" t="n">
         <v>4640</v>
       </c>
-      <c r="E5" t="n">
-        <v>624</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>396</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="G5" t="n">
+        <v>43</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>353</v>
+      </c>
+      <c r="J5" t="n">
+        <v>44</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +658,31 @@
       <c r="D6" t="n">
         <v>2316</v>
       </c>
-      <c r="E6" t="n">
-        <v>334</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G6" t="n">
+        <v>43</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>289</v>
       </c>
+      <c r="J6" t="n">
+        <v>44</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +699,31 @@
       <c r="D7" t="n">
         <v>3080</v>
       </c>
-      <c r="E7" t="n">
-        <v>595</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>228</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="G7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>422</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +740,15 @@
       <c r="D8" t="n">
         <v>5899</v>
       </c>
-      <c r="E8" t="n">
-        <v>216</v>
-      </c>
-      <c r="F8" t="n">
-        <v>56</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +765,15 @@
       <c r="D9" t="n">
         <v>581</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +790,31 @@
       <c r="D10" t="n">
         <v>7936</v>
       </c>
-      <c r="E10" t="n">
-        <v>1138</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>975</v>
-      </c>
+        <v>1216</v>
+      </c>
+      <c r="G10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1051</v>
+      </c>
+      <c r="J10" t="n">
+        <v>44</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +831,31 @@
       <c r="D11" t="n">
         <v>5300</v>
       </c>
-      <c r="E11" t="n">
-        <v>1165</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>249</v>
-      </c>
+        <v>1121</v>
+      </c>
+      <c r="G11" t="n">
+        <v>45</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>204</v>
+      </c>
+      <c r="J11" t="n">
+        <v>44</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +872,23 @@
       <c r="D12" t="n">
         <v>4776</v>
       </c>
-      <c r="E12" t="n">
-        <v>748</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
         <v>576</v>
       </c>
+      <c r="G12" t="n">
+        <v>45</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +905,23 @@
       <c r="D13" t="n">
         <v>7516</v>
       </c>
-      <c r="E13" t="n">
-        <v>1143</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>473</v>
-      </c>
+        <v>946</v>
+      </c>
+      <c r="G13" t="n">
+        <v>45</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +938,31 @@
       <c r="D14" t="n">
         <v>7012</v>
       </c>
-      <c r="E14" t="n">
-        <v>1143</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>700</v>
-      </c>
+        <v>1400</v>
+      </c>
+      <c r="G14" t="n">
+        <v>45</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1053</v>
+      </c>
+      <c r="J14" t="n">
+        <v>44</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +979,23 @@
       <c r="D15" t="n">
         <v>4704</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>598</v>
       </c>
-      <c r="F15" t="n">
-        <v>44</v>
-      </c>
+      <c r="G15" t="n">
+        <v>44</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1012,15 @@
       <c r="D16" t="n">
         <v>3132</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1037,15 @@
       <c r="D17" t="n">
         <v>3304</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1062,15 @@
       <c r="D18" t="n">
         <v>1720</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,11 +1087,38 @@
       <c r="D19" t="n">
         <v>3964</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>39</v>
+      </c>
+      <c r="G19" t="n">
+        <v>24</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>80</v>
+      </c>
+      <c r="J19" t="n">
+        <v>25</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
         <v>383</v>
       </c>
-      <c r="F19" t="n">
-        <v>296</v>
+      <c r="M19" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="20">
@@ -871,12 +1136,15 @@
       <c r="D20" t="n">
         <v>2068</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1161,23 @@
       <c r="D21" t="n">
         <v>10240</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>554</v>
       </c>
-      <c r="F21" t="n">
-        <v>44</v>
-      </c>
+      <c r="G21" t="n">
+        <v>44</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1194,23 @@
       <c r="D22" t="n">
         <v>1368</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>95</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>45</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1227,31 @@
       <c r="D23" t="n">
         <v>5028</v>
       </c>
-      <c r="E23" t="n">
-        <v>1139</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>207</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="G23" t="n">
+        <v>44</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1095</v>
+      </c>
+      <c r="J23" t="n">
+        <v>45</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1268,31 @@
       <c r="D24" t="n">
         <v>932</v>
       </c>
-      <c r="E24" t="n">
-        <v>208</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F24" t="n">
+        <v>47</v>
+      </c>
+      <c r="G24" t="n">
+        <v>25</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>95</v>
       </c>
+      <c r="J24" t="n">
+        <v>45</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1309,23 @@
       <c r="D25" t="n">
         <v>1636</v>
       </c>
-      <c r="E25" t="n">
-        <v>335</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F25" t="n">
         <v>160</v>
       </c>
+      <c r="G25" t="n">
+        <v>44</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1342,31 @@
       <c r="D26" t="n">
         <v>1820</v>
       </c>
-      <c r="E26" t="n">
-        <v>336</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F26" t="n">
-        <v>249</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="G26" t="n">
+        <v>44</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>205</v>
+      </c>
+      <c r="J26" t="n">
+        <v>44</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1383,31 @@
       <c r="D27" t="n">
         <v>2048</v>
       </c>
-      <c r="E27" t="n">
-        <v>310</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>290</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="G27" t="n">
+        <v>44</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>266</v>
+      </c>
+      <c r="J27" t="n">
+        <v>44</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1424,23 @@
       <c r="D28" t="n">
         <v>1576</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>148</v>
       </c>
-      <c r="F28" t="n">
-        <v>44</v>
-      </c>
+      <c r="G28" t="n">
+        <v>44</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
